--- a/老虎机数学入门-PartIII-Wild连线模型.xlsx
+++ b/老虎机数学入门-PartIII-Wild连线模型.xlsx
@@ -5323,6 +5323,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AD130" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -19259,5 +19262,8 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Q355" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/老虎机数学入门-PartIII-Wild连线模型.xlsx
+++ b/老虎机数学入门-PartIII-Wild连线模型.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="PartIII 转轮+WILD连线→RTP" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3610" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="168">
   <si>
     <t>老虎机数学入门 PART Ⅲ —— 首轮出现 WILD 的 RTP 计算模型</t>
   </si>
@@ -1241,7 +1241,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1330,6 +1330,39 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2340,2951 +2373,2951 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:10">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="32" t="s">
+      <c r="B18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="32" t="s">
+      <c r="A19" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:10">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="32" t="s">
+      <c r="B20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:10">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="32" t="s">
+      <c r="B21" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:10">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="32" t="s">
+      <c r="B22" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:10">
-      <c r="A23" s="35" t="s">
+      <c r="A23" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="32" t="s">
+      <c r="B23" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="32" t="s">
+      <c r="A24" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:10">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="32" t="s">
+      <c r="B25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:10">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="50" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:10">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="32" t="s">
+      <c r="B27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:10">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="32" t="s">
+      <c r="B28" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:10">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="32" t="s">
+      <c r="B29" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:10">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="32" t="s">
+      <c r="B30" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:10">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="32" t="s">
+      <c r="B31" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="32" t="s">
+      <c r="A32" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:10">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="32" t="s">
+      <c r="B33" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:10">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="32" t="s">
+      <c r="B34" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:10">
-      <c r="A35" s="38" t="s">
+      <c r="A35" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="39" t="s">
+      <c r="D35" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="39" t="s">
+      <c r="E35" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="39" t="s">
+      <c r="F35" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="32" t="s">
+      <c r="G35" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="14.5" spans="1:10">
-      <c r="A36" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="F36" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="G36" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="32" t="s">
+      <c r="A36" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="54">
+        <v>2</v>
+      </c>
+      <c r="C36" s="54">
+        <v>2</v>
+      </c>
+      <c r="D36" s="54">
+        <v>2</v>
+      </c>
+      <c r="E36" s="54">
+        <v>2</v>
+      </c>
+      <c r="F36" s="54">
+        <v>2</v>
+      </c>
+      <c r="G36" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="14.5" spans="1:10">
-      <c r="A37" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="G37" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="32" t="s">
+      <c r="A37" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="54">
+        <v>1</v>
+      </c>
+      <c r="C37" s="54">
+        <v>3</v>
+      </c>
+      <c r="D37" s="54">
+        <v>3</v>
+      </c>
+      <c r="E37" s="54">
+        <v>3</v>
+      </c>
+      <c r="F37" s="54">
+        <v>3</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="14.5" spans="1:10">
-      <c r="A38" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="G38" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="32" t="s">
+      <c r="A38" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="54">
+        <v>2</v>
+      </c>
+      <c r="C38" s="54">
+        <v>3</v>
+      </c>
+      <c r="D38" s="54">
+        <v>3</v>
+      </c>
+      <c r="E38" s="54">
+        <v>3</v>
+      </c>
+      <c r="F38" s="54">
+        <v>3</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="14.5" spans="1:10">
-      <c r="A39" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="32" t="s">
+      <c r="A39" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="54">
+        <v>4</v>
+      </c>
+      <c r="C39" s="54">
+        <v>5</v>
+      </c>
+      <c r="D39" s="54">
+        <v>4</v>
+      </c>
+      <c r="E39" s="54">
+        <v>4</v>
+      </c>
+      <c r="F39" s="54">
+        <v>4</v>
+      </c>
+      <c r="G39" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="14.5" spans="1:10">
-      <c r="A40" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="E40" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="32" t="s">
+      <c r="A40" s="53">
+        <v>10</v>
+      </c>
+      <c r="B40" s="54">
+        <v>5</v>
+      </c>
+      <c r="C40" s="54">
+        <v>3</v>
+      </c>
+      <c r="D40" s="54">
+        <v>4</v>
+      </c>
+      <c r="E40" s="54">
+        <v>4</v>
+      </c>
+      <c r="F40" s="54">
+        <v>4</v>
+      </c>
+      <c r="G40" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="14.5" spans="1:10">
-      <c r="A41" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="D41" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="E41" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G41" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="32" t="s">
+      <c r="A41" s="53">
+        <v>9</v>
+      </c>
+      <c r="B41" s="54">
+        <v>6</v>
+      </c>
+      <c r="C41" s="54">
+        <v>4</v>
+      </c>
+      <c r="D41" s="54">
+        <v>4</v>
+      </c>
+      <c r="E41" s="54">
+        <v>4</v>
+      </c>
+      <c r="F41" s="54">
+        <v>4</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="14.5" spans="1:10">
-      <c r="A42" s="40" t="s">
+      <c r="A42" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="F42" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="G42" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="32" t="s">
+      <c r="B42" s="54">
+        <v>20</v>
+      </c>
+      <c r="C42" s="54">
+        <v>20</v>
+      </c>
+      <c r="D42" s="54">
+        <v>20</v>
+      </c>
+      <c r="E42" s="54">
+        <v>20</v>
+      </c>
+      <c r="F42" s="54">
+        <v>20</v>
+      </c>
+      <c r="G42" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B43" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="32" t="s">
+      <c r="A43" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:10">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="32" t="s">
+      <c r="B44" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:10">
-      <c r="A45" s="38" t="s">
+      <c r="A45" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B45" s="39" t="s">
+      <c r="B45" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="39" t="s">
+      <c r="D45" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="32" t="s">
+      <c r="E45" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="14.5" spans="1:10">
-      <c r="A46" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="32" t="s">
+      <c r="A46" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="54">
+        <v>5</v>
+      </c>
+      <c r="C46" s="54">
+        <v>30</v>
+      </c>
+      <c r="D46" s="54">
+        <v>100</v>
+      </c>
+      <c r="E46" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="14.5" spans="1:10">
-      <c r="A47" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="D47" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="32" t="s">
+      <c r="A47" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="54">
+        <v>5</v>
+      </c>
+      <c r="C47" s="54">
+        <v>25</v>
+      </c>
+      <c r="D47" s="54">
+        <v>100</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" ht="14.5" spans="1:10">
-      <c r="A48" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C48" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="D48" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="E48" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="32" t="s">
+      <c r="A48" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="54">
+        <v>5</v>
+      </c>
+      <c r="C48" s="54">
+        <v>20</v>
+      </c>
+      <c r="D48" s="54">
+        <v>75</v>
+      </c>
+      <c r="E48" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="1:10">
-      <c r="A49" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="D49" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="E49" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="32" t="s">
+      <c r="A49" s="53">
+        <v>10</v>
+      </c>
+      <c r="B49" s="54">
+        <v>5</v>
+      </c>
+      <c r="C49" s="54">
+        <v>20</v>
+      </c>
+      <c r="D49" s="54">
+        <v>75</v>
+      </c>
+      <c r="E49" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="14.5" spans="1:10">
-      <c r="A50" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E50" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="32" t="s">
+      <c r="A50" s="53">
+        <v>9</v>
+      </c>
+      <c r="B50" s="54">
+        <v>5</v>
+      </c>
+      <c r="C50" s="54">
+        <v>10</v>
+      </c>
+      <c r="D50" s="54">
+        <v>50</v>
+      </c>
+      <c r="E50" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="14.5" spans="1:10">
-      <c r="A51" s="40" t="s">
+      <c r="A51" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="32" t="s">
+      <c r="B51" s="54">
+        <v>150</v>
+      </c>
+      <c r="C51" s="54">
+        <v>300</v>
+      </c>
+      <c r="D51" s="54">
+        <v>1000</v>
+      </c>
+      <c r="E51" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B52" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="32" t="s">
+      <c r="A52" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:10">
-      <c r="A53" s="34" t="s">
+      <c r="A53" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="32" t="s">
+      <c r="B53" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:10">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="32" t="s">
+      <c r="B54" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B55" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I55" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="32" t="s">
+      <c r="A55" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:10">
-      <c r="A56" s="36" t="s">
+      <c r="A56" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="B56" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I56" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J56" s="32" t="s">
+      <c r="B56" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I56" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J56" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" ht="17" customHeight="1" spans="1:10">
-      <c r="A57" s="42" t="s">
+      <c r="A57" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="B57" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="32" t="s">
+      <c r="B57" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:10">
-      <c r="A58" s="36" t="s">
+      <c r="A58" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="32" t="s">
+      <c r="B58" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="17" customHeight="1" spans="1:10">
-      <c r="A59" s="42" t="s">
+      <c r="A59" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="B59" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I59" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59" s="32" t="s">
+      <c r="B59" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:10">
-      <c r="A60" s="37" t="s">
+      <c r="A60" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B60" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="32" t="s">
+      <c r="B60" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:10">
-      <c r="A61" s="36" t="s">
+      <c r="A61" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="32" t="s">
+      <c r="B61" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:10">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C62" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="32" t="s">
+      <c r="B62" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:10">
-      <c r="A63" s="36" t="s">
+      <c r="A63" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="32" t="s">
+      <c r="B63" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:10">
-      <c r="A64" s="36" t="s">
+      <c r="A64" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B64" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I64" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J64" s="32" t="s">
+      <c r="B64" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H64" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:10">
-      <c r="A65" s="36" t="s">
+      <c r="A65" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="B65" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="32" t="s">
+      <c r="B65" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:10">
-      <c r="A66" s="36" t="s">
+      <c r="A66" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I66" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J66" s="32" t="s">
+      <c r="B66" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:10">
-      <c r="A67" s="36" t="s">
+      <c r="A67" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="B67" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I67" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J67" s="32" t="s">
+      <c r="B67" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:10">
-      <c r="A68" s="36" t="s">
+      <c r="A68" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="B68" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I68" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="32" t="s">
+      <c r="B68" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:10">
-      <c r="A69" s="36" t="s">
+      <c r="A69" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G69" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I69" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J69" s="32" t="s">
+      <c r="B69" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:10">
-      <c r="A70" s="36" t="s">
+      <c r="A70" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="B70" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E70" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G70" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I70" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J70" s="32" t="s">
+      <c r="B70" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H70" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I70" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J70" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:10">
-      <c r="A71" s="43" t="s">
+      <c r="A71" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="B71" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G71" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I71" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71" s="32" t="s">
+      <c r="B71" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I71" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" ht="17" customHeight="1" spans="1:10">
-      <c r="A72" s="42" t="s">
+      <c r="A72" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G72" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I72" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J72" s="32" t="s">
+      <c r="B72" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H72" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I72" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:10">
-      <c r="A73" s="37" t="s">
+      <c r="A73" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G73" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I73" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J73" s="32" t="s">
+      <c r="B73" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H73" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I73" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" spans="1:10">
-      <c r="A74" s="38" t="s">
+      <c r="A74" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="39" t="s">
+      <c r="B74" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="39" t="s">
+      <c r="C74" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="D74" s="39" t="s">
+      <c r="D74" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="E74" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G74" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I74" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J74" s="32" t="s">
+      <c r="E74" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H74" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I74" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="29" spans="1:10">
-      <c r="A75" s="40" t="s">
+      <c r="A75" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="40" t="s">
+      <c r="B75" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="C75" s="41" t="s">
+      <c r="C75" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="D75" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="E75" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H75" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I75" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J75" s="32" t="s">
+      <c r="D75" s="54">
+        <v>1000</v>
+      </c>
+      <c r="E75" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I75" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="76" ht="45" customHeight="1" spans="1:10">
-      <c r="A76" s="40" t="s">
+      <c r="A76" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="B76" s="40" t="s">
+      <c r="B76" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="C76" s="40" t="s">
+      <c r="C76" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="D76" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="E76" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G76" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H76" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I76" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J76" s="32" t="s">
+      <c r="D76" s="54">
+        <v>300</v>
+      </c>
+      <c r="E76" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H76" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I76" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J76" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" ht="45" customHeight="1" spans="1:10">
-      <c r="A77" s="40" t="s">
+      <c r="A77" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="B77" s="40" t="s">
+      <c r="B77" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="C77" s="40" t="s">
+      <c r="C77" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="D77" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="E77" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G77" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H77" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I77" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J77" s="32" t="s">
+      <c r="D77" s="54">
+        <v>150</v>
+      </c>
+      <c r="E77" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H77" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I77" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J77" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B78" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C78" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E78" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F78" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G78" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H78" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I78" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J78" s="32" t="s">
+      <c r="A78" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B78" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E78" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G78" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H78" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I78" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J78" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:10">
-      <c r="A79" s="43" t="s">
+      <c r="A79" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="B79" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C79" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D79" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E79" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G79" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H79" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I79" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J79" s="32" t="s">
+      <c r="B79" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C79" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E79" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G79" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H79" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I79" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J79" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:10">
-      <c r="A80" s="35" t="s">
+      <c r="A80" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="B80" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C80" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D80" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G80" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H80" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I80" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J80" s="32" t="s">
+      <c r="B80" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G80" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H80" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I80" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J80" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B81" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C81" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E81" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G81" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H81" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I81" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J81" s="32" t="s">
+      <c r="A81" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B81" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E81" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G81" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H81" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I81" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J81" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:10">
-      <c r="A82" s="36" t="s">
+      <c r="A82" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="B82" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C82" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E82" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G82" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H82" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I82" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J82" s="32" t="s">
+      <c r="B82" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E82" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G82" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H82" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I82" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J82" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:10">
-      <c r="A83" s="36" t="s">
+      <c r="A83" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="B83" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C83" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D83" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E83" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F83" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G83" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H83" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I83" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J83" s="32" t="s">
+      <c r="B83" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E83" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G83" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H83" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I83" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J83" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="84" ht="33" spans="1:10">
-      <c r="A84" s="36" t="s">
+      <c r="A84" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="B84" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E84" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F84" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G84" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H84" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I84" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J84" s="32" t="s">
+      <c r="B84" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E84" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G84" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H84" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I84" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J84" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:10">
-      <c r="A85" s="35" t="s">
+      <c r="A85" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="B85" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C85" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F85" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G85" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H85" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I85" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J85" s="32" t="s">
+      <c r="B85" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G85" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H85" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I85" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J85" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B86" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C86" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D86" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E86" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F86" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G86" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H86" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I86" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J86" s="32" t="s">
+      <c r="A86" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B86" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G86" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H86" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I86" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J86" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1" spans="1:10">
-      <c r="A87" s="38" t="s">
+      <c r="A87" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="B87" s="39" t="s">
+      <c r="B87" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="C87" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D87" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E87" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F87" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G87" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H87" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I87" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J87" s="32" t="s">
+      <c r="C87" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E87" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G87" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H87" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I87" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J87" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="88" ht="14.5" spans="1:10">
-      <c r="A88" s="40" t="s">
+      <c r="A88" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="B88" s="41" t="s">
+      <c r="B88" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="C88" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E88" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F88" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G88" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H88" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I88" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J88" s="32" t="s">
+      <c r="C88" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G88" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H88" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I88" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J88" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" ht="14.5" spans="1:10">
-      <c r="A89" s="40" t="s">
+      <c r="A89" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="B89" s="41" t="s">
+      <c r="B89" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="C89" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E89" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F89" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G89" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H89" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I89" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J89" s="32" t="s">
+      <c r="C89" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E89" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G89" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H89" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I89" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J89" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="90" ht="14.5" spans="1:10">
-      <c r="A90" s="40" t="s">
+      <c r="A90" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="B90" s="41" t="s">
+      <c r="B90" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="C90" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D90" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E90" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F90" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G90" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H90" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I90" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J90" s="32" t="s">
+      <c r="C90" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D90" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G90" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H90" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I90" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J90" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="91" ht="14.5" spans="1:10">
-      <c r="A91" s="40" t="s">
+      <c r="A91" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="B91" s="41" t="s">
+      <c r="B91" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="C91" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D91" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E91" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F91" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G91" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H91" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I91" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J91" s="32" t="s">
+      <c r="C91" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E91" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G91" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H91" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I91" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J91" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="92" ht="14.5" spans="1:10">
-      <c r="A92" s="40" t="s">
+      <c r="A92" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="B92" s="41" t="s">
+      <c r="B92" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="C92" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E92" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F92" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G92" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H92" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I92" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J92" s="32" t="s">
+      <c r="C92" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H92" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I92" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J92" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="93" ht="14.5" spans="1:10">
-      <c r="A93" s="40" t="s">
+      <c r="A93" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="B93" s="41" t="s">
+      <c r="B93" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="C93" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D93" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E93" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F93" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G93" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H93" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I93" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J93" s="32" t="s">
+      <c r="C93" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E93" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F93" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G93" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H93" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I93" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J93" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B94" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C94" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D94" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E94" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F94" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G94" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H94" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I94" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J94" s="32" t="s">
+      <c r="A94" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B94" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D94" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E94" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G94" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H94" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I94" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J94" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:10">
-      <c r="A95" s="35" t="s">
+      <c r="A95" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="B95" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C95" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D95" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E95" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F95" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G95" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H95" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I95" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J95" s="32" t="s">
+      <c r="B95" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D95" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G95" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H95" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I95" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J95" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B96" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D96" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E96" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F96" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G96" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H96" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I96" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J96" s="32" t="s">
+      <c r="A96" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B96" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D96" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G96" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H96" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I96" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J96" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:10">
-      <c r="A97" s="37" t="s">
+      <c r="A97" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="B97" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C97" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D97" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E97" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F97" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G97" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H97" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I97" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J97" s="32" t="s">
+      <c r="B97" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D97" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G97" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H97" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I97" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J97" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:10">
-      <c r="A98" s="35" t="s">
+      <c r="A98" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="B98" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C98" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D98" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E98" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F98" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G98" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H98" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I98" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J98" s="32" t="s">
+      <c r="B98" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D98" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E98" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G98" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H98" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I98" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J98" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B99" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C99" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D99" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E99" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F99" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G99" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H99" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I99" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J99" s="32" t="s">
+      <c r="A99" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B99" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D99" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E99" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G99" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H99" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I99" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J99" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1" spans="1:10">
-      <c r="A100" s="38" t="s">
+      <c r="A100" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="B100" s="39" t="s">
+      <c r="B100" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="C100" s="39" t="s">
+      <c r="C100" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="D100" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E100" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F100" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G100" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H100" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I100" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J100" s="32" t="s">
+      <c r="D100" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G100" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H100" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I100" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J100" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" ht="14.5" spans="1:10">
-      <c r="A101" s="40" t="s">
+      <c r="A101" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="B101" s="41" t="s">
+      <c r="B101" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="C101" s="41" t="s">
+      <c r="C101" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="D101" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E101" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F101" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G101" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I101" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J101" s="32" t="s">
+      <c r="D101" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E101" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G101" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="102" ht="14.5" spans="1:10">
-      <c r="A102" s="40" t="s">
+      <c r="A102" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="B102" s="41" t="s">
+      <c r="B102" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="C102" s="41" t="s">
+      <c r="C102" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="D102" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E102" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F102" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G102" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H102" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I102" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J102" s="32" t="s">
+      <c r="D102" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E102" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G102" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H102" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I102" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J102" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="103" ht="14.5" spans="1:10">
-      <c r="A103" s="40" t="s">
+      <c r="A103" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="B103" s="41" t="s">
+      <c r="B103" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="C103" s="41" t="s">
+      <c r="C103" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="D103" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E103" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F103" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G103" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H103" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I103" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J103" s="32" t="s">
+      <c r="D103" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E103" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G103" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H103" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I103" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J103" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="104" ht="14.5" spans="1:10">
-      <c r="A104" s="40" t="s">
+      <c r="A104" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="B104" s="41" t="s">
+      <c r="B104" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="C104" s="41" t="s">
+      <c r="C104" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="D104" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E104" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F104" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G104" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H104" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I104" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J104" s="32" t="s">
+      <c r="D104" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E104" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F104" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G104" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H104" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I104" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J104" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="105" ht="14.5" spans="1:10">
-      <c r="A105" s="40" t="s">
+      <c r="A105" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="B105" s="41" t="s">
+      <c r="B105" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="C105" s="41" t="s">
+      <c r="C105" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="D105" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E105" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F105" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G105" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H105" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I105" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J105" s="32" t="s">
+      <c r="D105" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E105" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G105" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H105" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I105" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J105" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B106" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C106" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D106" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E106" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F106" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G106" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H106" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I106" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J106" s="32" t="s">
+      <c r="A106" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B106" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C106" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D106" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E106" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G106" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H106" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I106" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J106" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:10">
-      <c r="A107" s="35" t="s">
+      <c r="A107" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="B107" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C107" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D107" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E107" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F107" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G107" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H107" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I107" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J107" s="32" t="s">
+      <c r="B107" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C107" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E107" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F107" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G107" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H107" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I107" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J107" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B108" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C108" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D108" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E108" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F108" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G108" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H108" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I108" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J108" s="32" t="s">
+      <c r="A108" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B108" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D108" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E108" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F108" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G108" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H108" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I108" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J108" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:10">
-      <c r="A109" s="36" t="s">
+      <c r="A109" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="B109" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C109" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D109" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E109" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F109" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G109" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H109" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I109" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J109" s="32" t="s">
+      <c r="B109" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C109" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D109" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E109" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F109" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G109" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H109" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I109" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J109" s="45" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:10">
-      <c r="A110" s="36" t="s">
+      <c r="A110" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="B110" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C110" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D110" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E110" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F110" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G110" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H110" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I110" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J110" s="32" t="s">
+      <c r="B110" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C110" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D110" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E110" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F110" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G110" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H110" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I110" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J110" s="45" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5537,8 +5570,8 @@
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:12">
-      <c r="A6" s="6" t="s">
-        <v>43</v>
+      <c r="A6" s="57">
+        <v>10</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
@@ -5575,8 +5608,8 @@
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:12">
-      <c r="A7" s="6" t="s">
-        <v>44</v>
+      <c r="A7" s="57">
+        <v>9</v>
       </c>
       <c r="B7" s="6">
         <v>5</v>
@@ -6224,8 +6257,8 @@
       <c r="A24" s="12">
         <v>10</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>43</v>
+      <c r="B24" s="57">
+        <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>40</v>
@@ -6262,8 +6295,8 @@
       <c r="A25" s="12">
         <v>11</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>43</v>
+      <c r="B25" s="57">
+        <v>10</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>40</v>
@@ -6300,8 +6333,8 @@
       <c r="A26" s="12">
         <v>12</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>43</v>
+      <c r="B26" s="57">
+        <v>10</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>40</v>
@@ -6338,20 +6371,20 @@
       <c r="A27" s="12">
         <v>13</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>43</v>
+      <c r="B27" s="57">
+        <v>10</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>43</v>
+      <c r="D27" s="57">
+        <v>10</v>
+      </c>
+      <c r="E27" s="57">
+        <v>10</v>
+      </c>
+      <c r="F27" s="57">
+        <v>10</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>1</v>
@@ -6376,20 +6409,20 @@
       <c r="A28" s="12">
         <v>14</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>43</v>
+      <c r="B28" s="57">
+        <v>10</v>
+      </c>
+      <c r="C28" s="57">
+        <v>10</v>
+      </c>
+      <c r="D28" s="57">
+        <v>10</v>
+      </c>
+      <c r="E28" s="57">
+        <v>10</v>
+      </c>
+      <c r="F28" s="57">
+        <v>10</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>1</v>
@@ -6414,20 +6447,20 @@
       <c r="A29" s="12">
         <v>15</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>43</v>
+      <c r="B29" s="57">
+        <v>9</v>
+      </c>
+      <c r="C29" s="57">
+        <v>10</v>
+      </c>
+      <c r="D29" s="57">
+        <v>10</v>
+      </c>
+      <c r="E29" s="57">
+        <v>10</v>
+      </c>
+      <c r="F29" s="57">
+        <v>10</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>1</v>
@@ -6452,20 +6485,20 @@
       <c r="A30" s="12">
         <v>16</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>43</v>
+      <c r="B30" s="57">
+        <v>9</v>
+      </c>
+      <c r="C30" s="57">
+        <v>10</v>
+      </c>
+      <c r="D30" s="57">
+        <v>10</v>
+      </c>
+      <c r="E30" s="57">
+        <v>10</v>
+      </c>
+      <c r="F30" s="57">
+        <v>10</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>1</v>
@@ -6490,20 +6523,20 @@
       <c r="A31" s="12">
         <v>17</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>44</v>
+      <c r="B31" s="57">
+        <v>9</v>
+      </c>
+      <c r="C31" s="57">
+        <v>9</v>
+      </c>
+      <c r="D31" s="57">
+        <v>9</v>
+      </c>
+      <c r="E31" s="57">
+        <v>9</v>
+      </c>
+      <c r="F31" s="57">
+        <v>9</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>1</v>
@@ -6528,20 +6561,20 @@
       <c r="A32" s="12">
         <v>18</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>44</v>
+      <c r="B32" s="57">
+        <v>9</v>
+      </c>
+      <c r="C32" s="57">
+        <v>9</v>
+      </c>
+      <c r="D32" s="57">
+        <v>9</v>
+      </c>
+      <c r="E32" s="57">
+        <v>9</v>
+      </c>
+      <c r="F32" s="57">
+        <v>9</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>1</v>
@@ -6566,20 +6599,20 @@
       <c r="A33" s="12">
         <v>19</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>44</v>
+      <c r="B33" s="57">
+        <v>9</v>
+      </c>
+      <c r="C33" s="57">
+        <v>9</v>
+      </c>
+      <c r="D33" s="57">
+        <v>9</v>
+      </c>
+      <c r="E33" s="57">
+        <v>9</v>
+      </c>
+      <c r="F33" s="57">
+        <v>9</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>1</v>
@@ -6604,20 +6637,20 @@
       <c r="A34" s="12">
         <v>20</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>44</v>
+      <c r="B34" s="57">
+        <v>9</v>
+      </c>
+      <c r="C34" s="57">
+        <v>9</v>
+      </c>
+      <c r="D34" s="57">
+        <v>9</v>
+      </c>
+      <c r="E34" s="57">
+        <v>9</v>
+      </c>
+      <c r="F34" s="57">
+        <v>9</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>1</v>
@@ -6925,8 +6958,8 @@
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:12">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
+      <c r="A42" s="57">
+        <v>10</v>
       </c>
       <c r="B42" s="12">
         <f t="shared" si="0"/>
@@ -6968,8 +7001,8 @@
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:12">
-      <c r="A43" s="6" t="s">
-        <v>44</v>
+      <c r="A43" s="57">
+        <v>9</v>
       </c>
       <c r="B43" s="12">
         <f t="shared" si="0"/>
@@ -7708,26 +7741,26 @@
       <c r="A61" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>43</v>
+      <c r="B61" s="58">
+        <v>10</v>
       </c>
       <c r="C61" s="10">
         <v>5</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>43</v>
+      <c r="D61" s="57">
+        <v>10</v>
+      </c>
+      <c r="E61" s="57">
+        <v>10</v>
+      </c>
+      <c r="F61" s="57">
+        <v>10</v>
+      </c>
+      <c r="G61" s="57">
+        <v>10</v>
+      </c>
+      <c r="H61" s="57">
+        <v>10</v>
       </c>
       <c r="I61" s="18">
         <f>PRODUCT($B$42,$C$42,$D$42,$E$42,$F$42)</f>
@@ -7750,23 +7783,23 @@
       <c r="A62" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>43</v>
+      <c r="B62" s="58">
+        <v>10</v>
       </c>
       <c r="C62" s="10">
         <v>4</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>43</v>
+      <c r="D62" s="57">
+        <v>10</v>
+      </c>
+      <c r="E62" s="57">
+        <v>10</v>
+      </c>
+      <c r="F62" s="57">
+        <v>10</v>
+      </c>
+      <c r="G62" s="57">
+        <v>10</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>163</v>
@@ -7792,20 +7825,20 @@
       <c r="A63" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>43</v>
+      <c r="B63" s="58">
+        <v>10</v>
       </c>
       <c r="C63" s="10">
         <v>3</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>43</v>
+      <c r="D63" s="57">
+        <v>10</v>
+      </c>
+      <c r="E63" s="57">
+        <v>10</v>
+      </c>
+      <c r="F63" s="57">
+        <v>10</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>163</v>
@@ -7834,26 +7867,26 @@
       <c r="A64" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>44</v>
+      <c r="B64" s="58">
+        <v>9</v>
       </c>
       <c r="C64" s="10">
         <v>5</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>44</v>
+      <c r="D64" s="57">
+        <v>9</v>
+      </c>
+      <c r="E64" s="57">
+        <v>9</v>
+      </c>
+      <c r="F64" s="57">
+        <v>9</v>
+      </c>
+      <c r="G64" s="57">
+        <v>9</v>
+      </c>
+      <c r="H64" s="57">
+        <v>9</v>
       </c>
       <c r="I64" s="18">
         <f>PRODUCT($B$43,$C$43,$D$43,$E$43,$F$43)</f>
@@ -7876,23 +7909,23 @@
       <c r="A65" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>44</v>
+      <c r="B65" s="58">
+        <v>9</v>
       </c>
       <c r="C65" s="10">
         <v>4</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>44</v>
+      <c r="D65" s="57">
+        <v>9</v>
+      </c>
+      <c r="E65" s="57">
+        <v>9</v>
+      </c>
+      <c r="F65" s="57">
+        <v>9</v>
+      </c>
+      <c r="G65" s="57">
+        <v>9</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>164</v>
@@ -7918,20 +7951,20 @@
       <c r="A66" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>44</v>
+      <c r="B66" s="58">
+        <v>9</v>
       </c>
       <c r="C66" s="10">
         <v>3</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>44</v>
+      <c r="D66" s="57">
+        <v>9</v>
+      </c>
+      <c r="E66" s="57">
+        <v>9</v>
+      </c>
+      <c r="F66" s="57">
+        <v>9</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>164</v>
@@ -14638,8 +14671,8 @@
       <c r="A226" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B226" s="10" t="s">
-        <v>43</v>
+      <c r="B226" s="58">
+        <v>10</v>
       </c>
       <c r="C226" s="10">
         <v>5</v>
@@ -14680,8 +14713,8 @@
       <c r="A227" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B227" s="10" t="s">
-        <v>43</v>
+      <c r="B227" s="58">
+        <v>10</v>
       </c>
       <c r="C227" s="10">
         <v>5</v>
@@ -14698,8 +14731,8 @@
       <c r="G227" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H227" s="6" t="s">
-        <v>43</v>
+      <c r="H227" s="57">
+        <v>10</v>
       </c>
       <c r="I227" s="18">
         <f>PRODUCT($B$38,$C$38,$D$38,$E$38,$F$42)</f>
@@ -14722,8 +14755,8 @@
       <c r="A228" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B228" s="10" t="s">
-        <v>43</v>
+      <c r="B228" s="58">
+        <v>10</v>
       </c>
       <c r="C228" s="10">
         <v>5</v>
@@ -14737,8 +14770,8 @@
       <c r="F228" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G228" s="6" t="s">
-        <v>43</v>
+      <c r="G228" s="57">
+        <v>10</v>
       </c>
       <c r="H228" s="7" t="s">
         <v>34</v>
@@ -14764,8 +14797,8 @@
       <c r="A229" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B229" s="10" t="s">
-        <v>43</v>
+      <c r="B229" s="58">
+        <v>10</v>
       </c>
       <c r="C229" s="10">
         <v>5</v>
@@ -14779,11 +14812,11 @@
       <c r="F229" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G229" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H229" s="6" t="s">
-        <v>43</v>
+      <c r="G229" s="57">
+        <v>10</v>
+      </c>
+      <c r="H229" s="57">
+        <v>10</v>
       </c>
       <c r="I229" s="18">
         <f>PRODUCT($B$38,$C$38,$D$38,$E$42,$F$42)</f>
@@ -14806,8 +14839,8 @@
       <c r="A230" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B230" s="10" t="s">
-        <v>43</v>
+      <c r="B230" s="58">
+        <v>10</v>
       </c>
       <c r="C230" s="10">
         <v>5</v>
@@ -14818,8 +14851,8 @@
       <c r="E230" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F230" s="6" t="s">
-        <v>43</v>
+      <c r="F230" s="57">
+        <v>10</v>
       </c>
       <c r="G230" s="7" t="s">
         <v>34</v>
@@ -14848,8 +14881,8 @@
       <c r="A231" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B231" s="10" t="s">
-        <v>43</v>
+      <c r="B231" s="58">
+        <v>10</v>
       </c>
       <c r="C231" s="10">
         <v>5</v>
@@ -14860,14 +14893,14 @@
       <c r="E231" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F231" s="6" t="s">
-        <v>43</v>
+      <c r="F231" s="57">
+        <v>10</v>
       </c>
       <c r="G231" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H231" s="6" t="s">
-        <v>43</v>
+      <c r="H231" s="57">
+        <v>10</v>
       </c>
       <c r="I231" s="18">
         <f>PRODUCT($B$38,$C$38,$D$42,$E$38,$F$42)</f>
@@ -14890,8 +14923,8 @@
       <c r="A232" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B232" s="10" t="s">
-        <v>43</v>
+      <c r="B232" s="58">
+        <v>10</v>
       </c>
       <c r="C232" s="10">
         <v>5</v>
@@ -14902,11 +14935,11 @@
       <c r="E232" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F232" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G232" s="6" t="s">
-        <v>43</v>
+      <c r="F232" s="57">
+        <v>10</v>
+      </c>
+      <c r="G232" s="57">
+        <v>10</v>
       </c>
       <c r="H232" s="7" t="s">
         <v>34</v>
@@ -14932,8 +14965,8 @@
       <c r="A233" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B233" s="10" t="s">
-        <v>43</v>
+      <c r="B233" s="58">
+        <v>10</v>
       </c>
       <c r="C233" s="10">
         <v>5</v>
@@ -14944,14 +14977,14 @@
       <c r="E233" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F233" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G233" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H233" s="6" t="s">
-        <v>43</v>
+      <c r="F233" s="57">
+        <v>10</v>
+      </c>
+      <c r="G233" s="57">
+        <v>10</v>
+      </c>
+      <c r="H233" s="57">
+        <v>10</v>
       </c>
       <c r="I233" s="18">
         <f>PRODUCT($B$38,$C$38,$D$42,$E$42,$F$42)</f>
@@ -14974,8 +15007,8 @@
       <c r="A234" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B234" s="10" t="s">
-        <v>43</v>
+      <c r="B234" s="58">
+        <v>10</v>
       </c>
       <c r="C234" s="10">
         <v>5</v>
@@ -14983,8 +15016,8 @@
       <c r="D234" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E234" s="6" t="s">
-        <v>43</v>
+      <c r="E234" s="57">
+        <v>10</v>
       </c>
       <c r="F234" s="7" t="s">
         <v>34</v>
@@ -15016,8 +15049,8 @@
       <c r="A235" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B235" s="10" t="s">
-        <v>43</v>
+      <c r="B235" s="58">
+        <v>10</v>
       </c>
       <c r="C235" s="10">
         <v>5</v>
@@ -15025,8 +15058,8 @@
       <c r="D235" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E235" s="6" t="s">
-        <v>43</v>
+      <c r="E235" s="57">
+        <v>10</v>
       </c>
       <c r="F235" s="7" t="s">
         <v>34</v>
@@ -15034,8 +15067,8 @@
       <c r="G235" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H235" s="6" t="s">
-        <v>43</v>
+      <c r="H235" s="57">
+        <v>10</v>
       </c>
       <c r="I235" s="18">
         <f>PRODUCT($B$38,$C$42,$D$38,$E$38,$F$42)</f>
@@ -15058,8 +15091,8 @@
       <c r="A236" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B236" s="10" t="s">
-        <v>43</v>
+      <c r="B236" s="58">
+        <v>10</v>
       </c>
       <c r="C236" s="10">
         <v>5</v>
@@ -15067,14 +15100,14 @@
       <c r="D236" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E236" s="6" t="s">
-        <v>43</v>
+      <c r="E236" s="57">
+        <v>10</v>
       </c>
       <c r="F236" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G236" s="6" t="s">
-        <v>43</v>
+      <c r="G236" s="57">
+        <v>10</v>
       </c>
       <c r="H236" s="7" t="s">
         <v>34</v>
@@ -15100,8 +15133,8 @@
       <c r="A237" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B237" s="10" t="s">
-        <v>43</v>
+      <c r="B237" s="58">
+        <v>10</v>
       </c>
       <c r="C237" s="10">
         <v>5</v>
@@ -15109,17 +15142,17 @@
       <c r="D237" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E237" s="6" t="s">
-        <v>43</v>
+      <c r="E237" s="57">
+        <v>10</v>
       </c>
       <c r="F237" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G237" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H237" s="6" t="s">
-        <v>43</v>
+      <c r="G237" s="57">
+        <v>10</v>
+      </c>
+      <c r="H237" s="57">
+        <v>10</v>
       </c>
       <c r="I237" s="18">
         <f>PRODUCT($B$38,$C$42,$D$38,$E$42,$F$42)</f>
@@ -15142,8 +15175,8 @@
       <c r="A238" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B238" s="10" t="s">
-        <v>43</v>
+      <c r="B238" s="58">
+        <v>10</v>
       </c>
       <c r="C238" s="10">
         <v>5</v>
@@ -15151,11 +15184,11 @@
       <c r="D238" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E238" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F238" s="6" t="s">
-        <v>43</v>
+      <c r="E238" s="57">
+        <v>10</v>
+      </c>
+      <c r="F238" s="57">
+        <v>10</v>
       </c>
       <c r="G238" s="7" t="s">
         <v>34</v>
@@ -15184,8 +15217,8 @@
       <c r="A239" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B239" s="10" t="s">
-        <v>43</v>
+      <c r="B239" s="58">
+        <v>10</v>
       </c>
       <c r="C239" s="10">
         <v>5</v>
@@ -15193,17 +15226,17 @@
       <c r="D239" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E239" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F239" s="6" t="s">
-        <v>43</v>
+      <c r="E239" s="57">
+        <v>10</v>
+      </c>
+      <c r="F239" s="57">
+        <v>10</v>
       </c>
       <c r="G239" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H239" s="6" t="s">
-        <v>43</v>
+      <c r="H239" s="57">
+        <v>10</v>
       </c>
       <c r="I239" s="18">
         <f>PRODUCT($B$38,$C$42,$D$42,$E$38,$F$42)</f>
@@ -15226,8 +15259,8 @@
       <c r="A240" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B240" s="10" t="s">
-        <v>43</v>
+      <c r="B240" s="58">
+        <v>10</v>
       </c>
       <c r="C240" s="10">
         <v>5</v>
@@ -15235,14 +15268,14 @@
       <c r="D240" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E240" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F240" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G240" s="6" t="s">
-        <v>43</v>
+      <c r="E240" s="57">
+        <v>10</v>
+      </c>
+      <c r="F240" s="57">
+        <v>10</v>
+      </c>
+      <c r="G240" s="57">
+        <v>10</v>
       </c>
       <c r="H240" s="7" t="s">
         <v>34</v>
@@ -15268,8 +15301,8 @@
       <c r="A241" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B241" s="10" t="s">
-        <v>43</v>
+      <c r="B241" s="58">
+        <v>10</v>
       </c>
       <c r="C241" s="10">
         <v>5</v>
@@ -15277,17 +15310,17 @@
       <c r="D241" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E241" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F241" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G241" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H241" s="6" t="s">
-        <v>43</v>
+      <c r="E241" s="57">
+        <v>10</v>
+      </c>
+      <c r="F241" s="57">
+        <v>10</v>
+      </c>
+      <c r="G241" s="57">
+        <v>10</v>
+      </c>
+      <c r="H241" s="57">
+        <v>10</v>
       </c>
       <c r="I241" s="18">
         <f>PRODUCT($B$38,$C$42,$D$42,$E$42,$F$42)</f>
@@ -15310,14 +15343,14 @@
       <c r="A242" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B242" s="10" t="s">
-        <v>43</v>
+      <c r="B242" s="58">
+        <v>10</v>
       </c>
       <c r="C242" s="10">
         <v>5</v>
       </c>
-      <c r="D242" s="6" t="s">
-        <v>43</v>
+      <c r="D242" s="57">
+        <v>10</v>
       </c>
       <c r="E242" s="7" t="s">
         <v>34</v>
@@ -15352,14 +15385,14 @@
       <c r="A243" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B243" s="10" t="s">
-        <v>43</v>
+      <c r="B243" s="58">
+        <v>10</v>
       </c>
       <c r="C243" s="10">
         <v>5</v>
       </c>
-      <c r="D243" s="6" t="s">
-        <v>43</v>
+      <c r="D243" s="57">
+        <v>10</v>
       </c>
       <c r="E243" s="7" t="s">
         <v>34</v>
@@ -15370,8 +15403,8 @@
       <c r="G243" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H243" s="6" t="s">
-        <v>43</v>
+      <c r="H243" s="57">
+        <v>10</v>
       </c>
       <c r="I243" s="18">
         <f>PRODUCT($B$42,$C$38,$D$38,$E$38,$F$42)</f>
@@ -15394,14 +15427,14 @@
       <c r="A244" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B244" s="10" t="s">
-        <v>43</v>
+      <c r="B244" s="58">
+        <v>10</v>
       </c>
       <c r="C244" s="10">
         <v>5</v>
       </c>
-      <c r="D244" s="6" t="s">
-        <v>43</v>
+      <c r="D244" s="57">
+        <v>10</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>34</v>
@@ -15409,8 +15442,8 @@
       <c r="F244" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G244" s="6" t="s">
-        <v>43</v>
+      <c r="G244" s="57">
+        <v>10</v>
       </c>
       <c r="H244" s="7" t="s">
         <v>34</v>
@@ -15436,14 +15469,14 @@
       <c r="A245" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B245" s="10" t="s">
-        <v>43</v>
+      <c r="B245" s="58">
+        <v>10</v>
       </c>
       <c r="C245" s="10">
         <v>5</v>
       </c>
-      <c r="D245" s="6" t="s">
-        <v>43</v>
+      <c r="D245" s="57">
+        <v>10</v>
       </c>
       <c r="E245" s="7" t="s">
         <v>34</v>
@@ -15451,11 +15484,11 @@
       <c r="F245" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G245" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H245" s="6" t="s">
-        <v>43</v>
+      <c r="G245" s="57">
+        <v>10</v>
+      </c>
+      <c r="H245" s="57">
+        <v>10</v>
       </c>
       <c r="I245" s="18">
         <f>PRODUCT($B$42,$C$38,$D$38,$E$42,$F$42)</f>
@@ -15478,20 +15511,20 @@
       <c r="A246" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B246" s="10" t="s">
-        <v>43</v>
+      <c r="B246" s="58">
+        <v>10</v>
       </c>
       <c r="C246" s="10">
         <v>5</v>
       </c>
-      <c r="D246" s="6" t="s">
-        <v>43</v>
+      <c r="D246" s="57">
+        <v>10</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F246" s="6" t="s">
-        <v>43</v>
+      <c r="F246" s="57">
+        <v>10</v>
       </c>
       <c r="G246" s="7" t="s">
         <v>34</v>
@@ -15520,26 +15553,26 @@
       <c r="A247" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B247" s="10" t="s">
-        <v>43</v>
+      <c r="B247" s="58">
+        <v>10</v>
       </c>
       <c r="C247" s="10">
         <v>5</v>
       </c>
-      <c r="D247" s="6" t="s">
-        <v>43</v>
+      <c r="D247" s="57">
+        <v>10</v>
       </c>
       <c r="E247" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F247" s="6" t="s">
-        <v>43</v>
+      <c r="F247" s="57">
+        <v>10</v>
       </c>
       <c r="G247" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H247" s="6" t="s">
-        <v>43</v>
+      <c r="H247" s="57">
+        <v>10</v>
       </c>
       <c r="I247" s="18">
         <f>PRODUCT($B$42,$C$38,$D$42,$E$38,$F$42)</f>
@@ -15562,23 +15595,23 @@
       <c r="A248" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B248" s="10" t="s">
-        <v>43</v>
+      <c r="B248" s="58">
+        <v>10</v>
       </c>
       <c r="C248" s="10">
         <v>5</v>
       </c>
-      <c r="D248" s="6" t="s">
-        <v>43</v>
+      <c r="D248" s="57">
+        <v>10</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F248" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G248" s="6" t="s">
-        <v>43</v>
+      <c r="F248" s="57">
+        <v>10</v>
+      </c>
+      <c r="G248" s="57">
+        <v>10</v>
       </c>
       <c r="H248" s="7" t="s">
         <v>34</v>
@@ -15604,26 +15637,26 @@
       <c r="A249" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B249" s="10" t="s">
-        <v>43</v>
+      <c r="B249" s="58">
+        <v>10</v>
       </c>
       <c r="C249" s="10">
         <v>5</v>
       </c>
-      <c r="D249" s="6" t="s">
-        <v>43</v>
+      <c r="D249" s="57">
+        <v>10</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F249" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G249" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H249" s="6" t="s">
-        <v>43</v>
+      <c r="F249" s="57">
+        <v>10</v>
+      </c>
+      <c r="G249" s="57">
+        <v>10</v>
+      </c>
+      <c r="H249" s="57">
+        <v>10</v>
       </c>
       <c r="I249" s="18">
         <f>PRODUCT($B$42,$C$38,$D$42,$E$42,$F$42)</f>
@@ -15646,17 +15679,17 @@
       <c r="A250" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B250" s="10" t="s">
-        <v>43</v>
+      <c r="B250" s="58">
+        <v>10</v>
       </c>
       <c r="C250" s="10">
         <v>5</v>
       </c>
-      <c r="D250" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E250" s="6" t="s">
-        <v>43</v>
+      <c r="D250" s="57">
+        <v>10</v>
+      </c>
+      <c r="E250" s="57">
+        <v>10</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>34</v>
@@ -15688,17 +15721,17 @@
       <c r="A251" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B251" s="10" t="s">
-        <v>43</v>
+      <c r="B251" s="58">
+        <v>10</v>
       </c>
       <c r="C251" s="10">
         <v>5</v>
       </c>
-      <c r="D251" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E251" s="6" t="s">
-        <v>43</v>
+      <c r="D251" s="57">
+        <v>10</v>
+      </c>
+      <c r="E251" s="57">
+        <v>10</v>
       </c>
       <c r="F251" s="7" t="s">
         <v>34</v>
@@ -15706,8 +15739,8 @@
       <c r="G251" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H251" s="6" t="s">
-        <v>43</v>
+      <c r="H251" s="57">
+        <v>10</v>
       </c>
       <c r="I251" s="18">
         <f>PRODUCT($B$42,$C$42,$D$38,$E$38,$F$42)</f>
@@ -15730,23 +15763,23 @@
       <c r="A252" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B252" s="10" t="s">
-        <v>43</v>
+      <c r="B252" s="58">
+        <v>10</v>
       </c>
       <c r="C252" s="10">
         <v>5</v>
       </c>
-      <c r="D252" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E252" s="6" t="s">
-        <v>43</v>
+      <c r="D252" s="57">
+        <v>10</v>
+      </c>
+      <c r="E252" s="57">
+        <v>10</v>
       </c>
       <c r="F252" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G252" s="6" t="s">
-        <v>43</v>
+      <c r="G252" s="57">
+        <v>10</v>
       </c>
       <c r="H252" s="7" t="s">
         <v>34</v>
@@ -15772,26 +15805,26 @@
       <c r="A253" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B253" s="10" t="s">
-        <v>43</v>
+      <c r="B253" s="58">
+        <v>10</v>
       </c>
       <c r="C253" s="10">
         <v>5</v>
       </c>
-      <c r="D253" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E253" s="6" t="s">
-        <v>43</v>
+      <c r="D253" s="57">
+        <v>10</v>
+      </c>
+      <c r="E253" s="57">
+        <v>10</v>
       </c>
       <c r="F253" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G253" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H253" s="6" t="s">
-        <v>43</v>
+      <c r="G253" s="57">
+        <v>10</v>
+      </c>
+      <c r="H253" s="57">
+        <v>10</v>
       </c>
       <c r="I253" s="18">
         <f>PRODUCT($B$42,$C$42,$D$38,$E$42,$F$42)</f>
@@ -15814,20 +15847,20 @@
       <c r="A254" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B254" s="10" t="s">
-        <v>43</v>
+      <c r="B254" s="58">
+        <v>10</v>
       </c>
       <c r="C254" s="10">
         <v>5</v>
       </c>
-      <c r="D254" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E254" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F254" s="6" t="s">
-        <v>43</v>
+      <c r="D254" s="57">
+        <v>10</v>
+      </c>
+      <c r="E254" s="57">
+        <v>10</v>
+      </c>
+      <c r="F254" s="57">
+        <v>10</v>
       </c>
       <c r="G254" s="7" t="s">
         <v>34</v>
@@ -15856,26 +15889,26 @@
       <c r="A255" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B255" s="10" t="s">
-        <v>43</v>
+      <c r="B255" s="58">
+        <v>10</v>
       </c>
       <c r="C255" s="10">
         <v>5</v>
       </c>
-      <c r="D255" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E255" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F255" s="6" t="s">
-        <v>43</v>
+      <c r="D255" s="57">
+        <v>10</v>
+      </c>
+      <c r="E255" s="57">
+        <v>10</v>
+      </c>
+      <c r="F255" s="57">
+        <v>10</v>
       </c>
       <c r="G255" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H255" s="6" t="s">
-        <v>43</v>
+      <c r="H255" s="57">
+        <v>10</v>
       </c>
       <c r="I255" s="18">
         <f>PRODUCT($B$42,$C$42,$D$42,$E$38,$F$42)</f>
@@ -15898,23 +15931,23 @@
       <c r="A256" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B256" s="10" t="s">
-        <v>43</v>
+      <c r="B256" s="58">
+        <v>10</v>
       </c>
       <c r="C256" s="10">
         <v>5</v>
       </c>
-      <c r="D256" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E256" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F256" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G256" s="6" t="s">
-        <v>43</v>
+      <c r="D256" s="57">
+        <v>10</v>
+      </c>
+      <c r="E256" s="57">
+        <v>10</v>
+      </c>
+      <c r="F256" s="57">
+        <v>10</v>
+      </c>
+      <c r="G256" s="57">
+        <v>10</v>
       </c>
       <c r="H256" s="7" t="s">
         <v>34</v>
@@ -15940,8 +15973,8 @@
       <c r="A257" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B257" s="10" t="s">
-        <v>43</v>
+      <c r="B257" s="58">
+        <v>10</v>
       </c>
       <c r="C257" s="10">
         <v>4</v>
@@ -15982,8 +16015,8 @@
       <c r="A258" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B258" s="10" t="s">
-        <v>43</v>
+      <c r="B258" s="58">
+        <v>10</v>
       </c>
       <c r="C258" s="10">
         <v>4</v>
@@ -15997,8 +16030,8 @@
       <c r="F258" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G258" s="6" t="s">
-        <v>43</v>
+      <c r="G258" s="57">
+        <v>10</v>
       </c>
       <c r="H258" s="7" t="s">
         <v>163</v>
@@ -16024,8 +16057,8 @@
       <c r="A259" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B259" s="10" t="s">
-        <v>43</v>
+      <c r="B259" s="58">
+        <v>10</v>
       </c>
       <c r="C259" s="10">
         <v>4</v>
@@ -16036,8 +16069,8 @@
       <c r="E259" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F259" s="6" t="s">
-        <v>43</v>
+      <c r="F259" s="57">
+        <v>10</v>
       </c>
       <c r="G259" s="7" t="s">
         <v>34</v>
@@ -16066,8 +16099,8 @@
       <c r="A260" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B260" s="10" t="s">
-        <v>43</v>
+      <c r="B260" s="58">
+        <v>10</v>
       </c>
       <c r="C260" s="10">
         <v>4</v>
@@ -16078,11 +16111,11 @@
       <c r="E260" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F260" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G260" s="6" t="s">
-        <v>43</v>
+      <c r="F260" s="57">
+        <v>10</v>
+      </c>
+      <c r="G260" s="57">
+        <v>10</v>
       </c>
       <c r="H260" s="7" t="s">
         <v>163</v>
@@ -16108,8 +16141,8 @@
       <c r="A261" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B261" s="10" t="s">
-        <v>43</v>
+      <c r="B261" s="58">
+        <v>10</v>
       </c>
       <c r="C261" s="10">
         <v>4</v>
@@ -16117,8 +16150,8 @@
       <c r="D261" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E261" s="6" t="s">
-        <v>43</v>
+      <c r="E261" s="57">
+        <v>10</v>
       </c>
       <c r="F261" s="7" t="s">
         <v>34</v>
@@ -16150,8 +16183,8 @@
       <c r="A262" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B262" s="10" t="s">
-        <v>43</v>
+      <c r="B262" s="58">
+        <v>10</v>
       </c>
       <c r="C262" s="10">
         <v>4</v>
@@ -16159,14 +16192,14 @@
       <c r="D262" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E262" s="6" t="s">
-        <v>43</v>
+      <c r="E262" s="57">
+        <v>10</v>
       </c>
       <c r="F262" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G262" s="6" t="s">
-        <v>43</v>
+      <c r="G262" s="57">
+        <v>10</v>
       </c>
       <c r="H262" s="7" t="s">
         <v>163</v>
@@ -16192,8 +16225,8 @@
       <c r="A263" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B263" s="10" t="s">
-        <v>43</v>
+      <c r="B263" s="58">
+        <v>10</v>
       </c>
       <c r="C263" s="10">
         <v>4</v>
@@ -16201,11 +16234,11 @@
       <c r="D263" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E263" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F263" s="6" t="s">
-        <v>43</v>
+      <c r="E263" s="57">
+        <v>10</v>
+      </c>
+      <c r="F263" s="57">
+        <v>10</v>
       </c>
       <c r="G263" s="7" t="s">
         <v>34</v>
@@ -16234,8 +16267,8 @@
       <c r="A264" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B264" s="10" t="s">
-        <v>43</v>
+      <c r="B264" s="58">
+        <v>10</v>
       </c>
       <c r="C264" s="10">
         <v>4</v>
@@ -16243,14 +16276,14 @@
       <c r="D264" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E264" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F264" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G264" s="6" t="s">
-        <v>43</v>
+      <c r="E264" s="57">
+        <v>10</v>
+      </c>
+      <c r="F264" s="57">
+        <v>10</v>
+      </c>
+      <c r="G264" s="57">
+        <v>10</v>
       </c>
       <c r="H264" s="7" t="s">
         <v>163</v>
@@ -16276,14 +16309,14 @@
       <c r="A265" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B265" s="10" t="s">
-        <v>43</v>
+      <c r="B265" s="58">
+        <v>10</v>
       </c>
       <c r="C265" s="10">
         <v>4</v>
       </c>
-      <c r="D265" s="6" t="s">
-        <v>43</v>
+      <c r="D265" s="57">
+        <v>10</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>34</v>
@@ -16318,14 +16351,14 @@
       <c r="A266" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B266" s="10" t="s">
-        <v>43</v>
+      <c r="B266" s="58">
+        <v>10</v>
       </c>
       <c r="C266" s="10">
         <v>4</v>
       </c>
-      <c r="D266" s="6" t="s">
-        <v>43</v>
+      <c r="D266" s="57">
+        <v>10</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>34</v>
@@ -16333,8 +16366,8 @@
       <c r="F266" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G266" s="6" t="s">
-        <v>43</v>
+      <c r="G266" s="57">
+        <v>10</v>
       </c>
       <c r="H266" s="7" t="s">
         <v>163</v>
@@ -16360,20 +16393,20 @@
       <c r="A267" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B267" s="10" t="s">
-        <v>43</v>
+      <c r="B267" s="58">
+        <v>10</v>
       </c>
       <c r="C267" s="10">
         <v>4</v>
       </c>
-      <c r="D267" s="6" t="s">
-        <v>43</v>
+      <c r="D267" s="57">
+        <v>10</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F267" s="6" t="s">
-        <v>43</v>
+      <c r="F267" s="57">
+        <v>10</v>
       </c>
       <c r="G267" s="7" t="s">
         <v>34</v>
@@ -16402,23 +16435,23 @@
       <c r="A268" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B268" s="10" t="s">
-        <v>43</v>
+      <c r="B268" s="58">
+        <v>10</v>
       </c>
       <c r="C268" s="10">
         <v>4</v>
       </c>
-      <c r="D268" s="6" t="s">
-        <v>43</v>
+      <c r="D268" s="57">
+        <v>10</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F268" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G268" s="6" t="s">
-        <v>43</v>
+      <c r="F268" s="57">
+        <v>10</v>
+      </c>
+      <c r="G268" s="57">
+        <v>10</v>
       </c>
       <c r="H268" s="7" t="s">
         <v>163</v>
@@ -16444,17 +16477,17 @@
       <c r="A269" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B269" s="10" t="s">
-        <v>43</v>
+      <c r="B269" s="58">
+        <v>10</v>
       </c>
       <c r="C269" s="10">
         <v>4</v>
       </c>
-      <c r="D269" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E269" s="6" t="s">
-        <v>43</v>
+      <c r="D269" s="57">
+        <v>10</v>
+      </c>
+      <c r="E269" s="57">
+        <v>10</v>
       </c>
       <c r="F269" s="7" t="s">
         <v>34</v>
@@ -16486,23 +16519,23 @@
       <c r="A270" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B270" s="10" t="s">
-        <v>43</v>
+      <c r="B270" s="58">
+        <v>10</v>
       </c>
       <c r="C270" s="10">
         <v>4</v>
       </c>
-      <c r="D270" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E270" s="6" t="s">
-        <v>43</v>
+      <c r="D270" s="57">
+        <v>10</v>
+      </c>
+      <c r="E270" s="57">
+        <v>10</v>
       </c>
       <c r="F270" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G270" s="6" t="s">
-        <v>43</v>
+      <c r="G270" s="57">
+        <v>10</v>
       </c>
       <c r="H270" s="7" t="s">
         <v>163</v>
@@ -16528,20 +16561,20 @@
       <c r="A271" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B271" s="10" t="s">
-        <v>43</v>
+      <c r="B271" s="58">
+        <v>10</v>
       </c>
       <c r="C271" s="10">
         <v>4</v>
       </c>
-      <c r="D271" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E271" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F271" s="6" t="s">
-        <v>43</v>
+      <c r="D271" s="57">
+        <v>10</v>
+      </c>
+      <c r="E271" s="57">
+        <v>10</v>
+      </c>
+      <c r="F271" s="57">
+        <v>10</v>
       </c>
       <c r="G271" s="7" t="s">
         <v>34</v>
@@ -16570,8 +16603,8 @@
       <c r="A272" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B272" s="10" t="s">
-        <v>43</v>
+      <c r="B272" s="58">
+        <v>10</v>
       </c>
       <c r="C272" s="10">
         <v>3</v>
@@ -16612,8 +16645,8 @@
       <c r="A273" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B273" s="10" t="s">
-        <v>43</v>
+      <c r="B273" s="58">
+        <v>10</v>
       </c>
       <c r="C273" s="10">
         <v>3</v>
@@ -16624,8 +16657,8 @@
       <c r="E273" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F273" s="6" t="s">
-        <v>43</v>
+      <c r="F273" s="57">
+        <v>10</v>
       </c>
       <c r="G273" s="7" t="s">
         <v>163</v>
@@ -16654,8 +16687,8 @@
       <c r="A274" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B274" s="10" t="s">
-        <v>43</v>
+      <c r="B274" s="58">
+        <v>10</v>
       </c>
       <c r="C274" s="10">
         <v>3</v>
@@ -16663,8 +16696,8 @@
       <c r="D274" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E274" s="6" t="s">
-        <v>43</v>
+      <c r="E274" s="57">
+        <v>10</v>
       </c>
       <c r="F274" s="7" t="s">
         <v>34</v>
@@ -16696,8 +16729,8 @@
       <c r="A275" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B275" s="10" t="s">
-        <v>43</v>
+      <c r="B275" s="58">
+        <v>10</v>
       </c>
       <c r="C275" s="10">
         <v>3</v>
@@ -16705,11 +16738,11 @@
       <c r="D275" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E275" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F275" s="6" t="s">
-        <v>43</v>
+      <c r="E275" s="57">
+        <v>10</v>
+      </c>
+      <c r="F275" s="57">
+        <v>10</v>
       </c>
       <c r="G275" s="7" t="s">
         <v>163</v>
@@ -16738,14 +16771,14 @@
       <c r="A276" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B276" s="10" t="s">
-        <v>43</v>
+      <c r="B276" s="58">
+        <v>10</v>
       </c>
       <c r="C276" s="10">
         <v>3</v>
       </c>
-      <c r="D276" s="6" t="s">
-        <v>43</v>
+      <c r="D276" s="57">
+        <v>10</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>34</v>
@@ -16780,20 +16813,20 @@
       <c r="A277" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B277" s="10" t="s">
-        <v>43</v>
+      <c r="B277" s="58">
+        <v>10</v>
       </c>
       <c r="C277" s="10">
         <v>3</v>
       </c>
-      <c r="D277" s="6" t="s">
-        <v>43</v>
+      <c r="D277" s="57">
+        <v>10</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F277" s="6" t="s">
-        <v>43</v>
+      <c r="F277" s="57">
+        <v>10</v>
       </c>
       <c r="G277" s="7" t="s">
         <v>163</v>
@@ -16822,17 +16855,17 @@
       <c r="A278" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B278" s="10" t="s">
-        <v>43</v>
+      <c r="B278" s="58">
+        <v>10</v>
       </c>
       <c r="C278" s="10">
         <v>3</v>
       </c>
-      <c r="D278" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E278" s="6" t="s">
-        <v>43</v>
+      <c r="D278" s="57">
+        <v>10</v>
+      </c>
+      <c r="E278" s="57">
+        <v>10</v>
       </c>
       <c r="F278" s="7" t="s">
         <v>34</v>
@@ -16864,8 +16897,8 @@
       <c r="A279" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B279" s="10" t="s">
-        <v>44</v>
+      <c r="B279" s="58">
+        <v>9</v>
       </c>
       <c r="C279" s="10">
         <v>5</v>
@@ -16906,8 +16939,8 @@
       <c r="A280" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B280" s="10" t="s">
-        <v>44</v>
+      <c r="B280" s="58">
+        <v>9</v>
       </c>
       <c r="C280" s="10">
         <v>5</v>
@@ -16924,8 +16957,8 @@
       <c r="G280" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H280" s="6" t="s">
-        <v>44</v>
+      <c r="H280" s="57">
+        <v>9</v>
       </c>
       <c r="I280" s="18">
         <f>PRODUCT($B$38,$C$38,$D$38,$E$38,$F$43)</f>
@@ -16948,8 +16981,8 @@
       <c r="A281" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B281" s="10" t="s">
-        <v>44</v>
+      <c r="B281" s="58">
+        <v>9</v>
       </c>
       <c r="C281" s="10">
         <v>5</v>
@@ -16963,8 +16996,8 @@
       <c r="F281" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G281" s="6" t="s">
-        <v>44</v>
+      <c r="G281" s="57">
+        <v>9</v>
       </c>
       <c r="H281" s="7" t="s">
         <v>34</v>
@@ -16990,8 +17023,8 @@
       <c r="A282" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B282" s="10" t="s">
-        <v>44</v>
+      <c r="B282" s="58">
+        <v>9</v>
       </c>
       <c r="C282" s="10">
         <v>5</v>
@@ -17005,11 +17038,11 @@
       <c r="F282" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G282" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H282" s="6" t="s">
-        <v>44</v>
+      <c r="G282" s="57">
+        <v>9</v>
+      </c>
+      <c r="H282" s="57">
+        <v>9</v>
       </c>
       <c r="I282" s="18">
         <f>PRODUCT($B$38,$C$38,$D$38,$E$43,$F$43)</f>
@@ -17032,8 +17065,8 @@
       <c r="A283" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B283" s="10" t="s">
-        <v>44</v>
+      <c r="B283" s="58">
+        <v>9</v>
       </c>
       <c r="C283" s="10">
         <v>5</v>
@@ -17044,8 +17077,8 @@
       <c r="E283" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F283" s="6" t="s">
-        <v>44</v>
+      <c r="F283" s="57">
+        <v>9</v>
       </c>
       <c r="G283" s="7" t="s">
         <v>34</v>
@@ -17074,8 +17107,8 @@
       <c r="A284" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B284" s="10" t="s">
-        <v>44</v>
+      <c r="B284" s="58">
+        <v>9</v>
       </c>
       <c r="C284" s="10">
         <v>5</v>
@@ -17086,14 +17119,14 @@
       <c r="E284" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F284" s="6" t="s">
-        <v>44</v>
+      <c r="F284" s="57">
+        <v>9</v>
       </c>
       <c r="G284" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H284" s="6" t="s">
-        <v>44</v>
+      <c r="H284" s="57">
+        <v>9</v>
       </c>
       <c r="I284" s="18">
         <f>PRODUCT($B$38,$C$38,$D$43,$E$38,$F$43)</f>
@@ -17116,8 +17149,8 @@
       <c r="A285" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B285" s="10" t="s">
-        <v>44</v>
+      <c r="B285" s="58">
+        <v>9</v>
       </c>
       <c r="C285" s="10">
         <v>5</v>
@@ -17128,11 +17161,11 @@
       <c r="E285" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F285" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G285" s="6" t="s">
-        <v>44</v>
+      <c r="F285" s="57">
+        <v>9</v>
+      </c>
+      <c r="G285" s="57">
+        <v>9</v>
       </c>
       <c r="H285" s="7" t="s">
         <v>34</v>
@@ -17158,8 +17191,8 @@
       <c r="A286" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B286" s="10" t="s">
-        <v>44</v>
+      <c r="B286" s="58">
+        <v>9</v>
       </c>
       <c r="C286" s="10">
         <v>5</v>
@@ -17170,14 +17203,14 @@
       <c r="E286" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F286" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G286" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H286" s="6" t="s">
-        <v>44</v>
+      <c r="F286" s="57">
+        <v>9</v>
+      </c>
+      <c r="G286" s="57">
+        <v>9</v>
+      </c>
+      <c r="H286" s="57">
+        <v>9</v>
       </c>
       <c r="I286" s="18">
         <f>PRODUCT($B$38,$C$38,$D$43,$E$43,$F$43)</f>
@@ -17200,8 +17233,8 @@
       <c r="A287" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B287" s="10" t="s">
-        <v>44</v>
+      <c r="B287" s="58">
+        <v>9</v>
       </c>
       <c r="C287" s="10">
         <v>5</v>
@@ -17209,8 +17242,8 @@
       <c r="D287" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E287" s="6" t="s">
-        <v>44</v>
+      <c r="E287" s="57">
+        <v>9</v>
       </c>
       <c r="F287" s="7" t="s">
         <v>34</v>
@@ -17242,8 +17275,8 @@
       <c r="A288" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B288" s="10" t="s">
-        <v>44</v>
+      <c r="B288" s="58">
+        <v>9</v>
       </c>
       <c r="C288" s="10">
         <v>5</v>
@@ -17251,8 +17284,8 @@
       <c r="D288" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E288" s="6" t="s">
-        <v>44</v>
+      <c r="E288" s="57">
+        <v>9</v>
       </c>
       <c r="F288" s="7" t="s">
         <v>34</v>
@@ -17260,8 +17293,8 @@
       <c r="G288" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H288" s="6" t="s">
-        <v>44</v>
+      <c r="H288" s="57">
+        <v>9</v>
       </c>
       <c r="I288" s="18">
         <f>PRODUCT($B$38,$C$43,$D$38,$E$38,$F$43)</f>
@@ -17284,8 +17317,8 @@
       <c r="A289" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B289" s="10" t="s">
-        <v>44</v>
+      <c r="B289" s="58">
+        <v>9</v>
       </c>
       <c r="C289" s="10">
         <v>5</v>
@@ -17293,14 +17326,14 @@
       <c r="D289" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E289" s="6" t="s">
-        <v>44</v>
+      <c r="E289" s="57">
+        <v>9</v>
       </c>
       <c r="F289" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G289" s="6" t="s">
-        <v>44</v>
+      <c r="G289" s="57">
+        <v>9</v>
       </c>
       <c r="H289" s="7" t="s">
         <v>34</v>
@@ -17326,8 +17359,8 @@
       <c r="A290" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B290" s="10" t="s">
-        <v>44</v>
+      <c r="B290" s="58">
+        <v>9</v>
       </c>
       <c r="C290" s="10">
         <v>5</v>
@@ -17335,17 +17368,17 @@
       <c r="D290" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E290" s="6" t="s">
-        <v>44</v>
+      <c r="E290" s="57">
+        <v>9</v>
       </c>
       <c r="F290" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G290" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H290" s="6" t="s">
-        <v>44</v>
+      <c r="G290" s="57">
+        <v>9</v>
+      </c>
+      <c r="H290" s="57">
+        <v>9</v>
       </c>
       <c r="I290" s="18">
         <f>PRODUCT($B$38,$C$43,$D$38,$E$43,$F$43)</f>
@@ -17368,8 +17401,8 @@
       <c r="A291" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B291" s="10" t="s">
-        <v>44</v>
+      <c r="B291" s="58">
+        <v>9</v>
       </c>
       <c r="C291" s="10">
         <v>5</v>
@@ -17377,11 +17410,11 @@
       <c r="D291" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E291" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F291" s="6" t="s">
-        <v>44</v>
+      <c r="E291" s="57">
+        <v>9</v>
+      </c>
+      <c r="F291" s="57">
+        <v>9</v>
       </c>
       <c r="G291" s="7" t="s">
         <v>34</v>
@@ -17410,8 +17443,8 @@
       <c r="A292" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B292" s="10" t="s">
-        <v>44</v>
+      <c r="B292" s="58">
+        <v>9</v>
       </c>
       <c r="C292" s="10">
         <v>5</v>
@@ -17419,17 +17452,17 @@
       <c r="D292" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E292" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F292" s="6" t="s">
-        <v>44</v>
+      <c r="E292" s="57">
+        <v>9</v>
+      </c>
+      <c r="F292" s="57">
+        <v>9</v>
       </c>
       <c r="G292" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H292" s="6" t="s">
-        <v>44</v>
+      <c r="H292" s="57">
+        <v>9</v>
       </c>
       <c r="I292" s="18">
         <f>PRODUCT($B$38,$C$43,$D$43,$E$38,$F$43)</f>
@@ -17452,8 +17485,8 @@
       <c r="A293" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B293" s="10" t="s">
-        <v>44</v>
+      <c r="B293" s="58">
+        <v>9</v>
       </c>
       <c r="C293" s="10">
         <v>5</v>
@@ -17461,14 +17494,14 @@
       <c r="D293" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E293" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F293" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G293" s="6" t="s">
-        <v>44</v>
+      <c r="E293" s="57">
+        <v>9</v>
+      </c>
+      <c r="F293" s="57">
+        <v>9</v>
+      </c>
+      <c r="G293" s="57">
+        <v>9</v>
       </c>
       <c r="H293" s="7" t="s">
         <v>34</v>
@@ -17494,8 +17527,8 @@
       <c r="A294" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B294" s="10" t="s">
-        <v>44</v>
+      <c r="B294" s="58">
+        <v>9</v>
       </c>
       <c r="C294" s="10">
         <v>5</v>
@@ -17503,17 +17536,17 @@
       <c r="D294" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E294" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F294" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G294" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H294" s="6" t="s">
-        <v>44</v>
+      <c r="E294" s="57">
+        <v>9</v>
+      </c>
+      <c r="F294" s="57">
+        <v>9</v>
+      </c>
+      <c r="G294" s="57">
+        <v>9</v>
+      </c>
+      <c r="H294" s="57">
+        <v>9</v>
       </c>
       <c r="I294" s="18">
         <f>PRODUCT($B$38,$C$43,$D$43,$E$43,$F$43)</f>
@@ -17536,14 +17569,14 @@
       <c r="A295" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B295" s="10" t="s">
-        <v>44</v>
+      <c r="B295" s="58">
+        <v>9</v>
       </c>
       <c r="C295" s="10">
         <v>5</v>
       </c>
-      <c r="D295" s="6" t="s">
-        <v>44</v>
+      <c r="D295" s="57">
+        <v>9</v>
       </c>
       <c r="E295" s="7" t="s">
         <v>34</v>
@@ -17578,14 +17611,14 @@
       <c r="A296" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B296" s="10" t="s">
-        <v>44</v>
+      <c r="B296" s="58">
+        <v>9</v>
       </c>
       <c r="C296" s="10">
         <v>5</v>
       </c>
-      <c r="D296" s="6" t="s">
-        <v>44</v>
+      <c r="D296" s="57">
+        <v>9</v>
       </c>
       <c r="E296" s="7" t="s">
         <v>34</v>
@@ -17596,8 +17629,8 @@
       <c r="G296" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H296" s="6" t="s">
-        <v>44</v>
+      <c r="H296" s="57">
+        <v>9</v>
       </c>
       <c r="I296" s="18">
         <f>PRODUCT($B$43,$C$38,$D$38,$E$38,$F$43)</f>
@@ -17620,14 +17653,14 @@
       <c r="A297" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B297" s="10" t="s">
-        <v>44</v>
+      <c r="B297" s="58">
+        <v>9</v>
       </c>
       <c r="C297" s="10">
         <v>5</v>
       </c>
-      <c r="D297" s="6" t="s">
-        <v>44</v>
+      <c r="D297" s="57">
+        <v>9</v>
       </c>
       <c r="E297" s="7" t="s">
         <v>34</v>
@@ -17635,8 +17668,8 @@
       <c r="F297" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G297" s="6" t="s">
-        <v>44</v>
+      <c r="G297" s="57">
+        <v>9</v>
       </c>
       <c r="H297" s="7" t="s">
         <v>34</v>
@@ -17662,14 +17695,14 @@
       <c r="A298" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B298" s="10" t="s">
-        <v>44</v>
+      <c r="B298" s="58">
+        <v>9</v>
       </c>
       <c r="C298" s="10">
         <v>5</v>
       </c>
-      <c r="D298" s="6" t="s">
-        <v>44</v>
+      <c r="D298" s="57">
+        <v>9</v>
       </c>
       <c r="E298" s="7" t="s">
         <v>34</v>
@@ -17677,11 +17710,11 @@
       <c r="F298" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G298" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H298" s="6" t="s">
-        <v>44</v>
+      <c r="G298" s="57">
+        <v>9</v>
+      </c>
+      <c r="H298" s="57">
+        <v>9</v>
       </c>
       <c r="I298" s="18">
         <f>PRODUCT($B$43,$C$38,$D$38,$E$43,$F$43)</f>
@@ -17704,20 +17737,20 @@
       <c r="A299" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B299" s="10" t="s">
-        <v>44</v>
+      <c r="B299" s="58">
+        <v>9</v>
       </c>
       <c r="C299" s="10">
         <v>5</v>
       </c>
-      <c r="D299" s="6" t="s">
-        <v>44</v>
+      <c r="D299" s="57">
+        <v>9</v>
       </c>
       <c r="E299" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F299" s="6" t="s">
-        <v>44</v>
+      <c r="F299" s="57">
+        <v>9</v>
       </c>
       <c r="G299" s="7" t="s">
         <v>34</v>
@@ -17746,26 +17779,26 @@
       <c r="A300" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B300" s="10" t="s">
-        <v>44</v>
+      <c r="B300" s="58">
+        <v>9</v>
       </c>
       <c r="C300" s="10">
         <v>5</v>
       </c>
-      <c r="D300" s="6" t="s">
-        <v>44</v>
+      <c r="D300" s="57">
+        <v>9</v>
       </c>
       <c r="E300" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F300" s="6" t="s">
-        <v>44</v>
+      <c r="F300" s="57">
+        <v>9</v>
       </c>
       <c r="G300" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H300" s="6" t="s">
-        <v>44</v>
+      <c r="H300" s="57">
+        <v>9</v>
       </c>
       <c r="I300" s="18">
         <f>PRODUCT($B$43,$C$38,$D$43,$E$38,$F$43)</f>
@@ -17788,23 +17821,23 @@
       <c r="A301" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B301" s="10" t="s">
-        <v>44</v>
+      <c r="B301" s="58">
+        <v>9</v>
       </c>
       <c r="C301" s="10">
         <v>5</v>
       </c>
-      <c r="D301" s="6" t="s">
-        <v>44</v>
+      <c r="D301" s="57">
+        <v>9</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F301" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G301" s="6" t="s">
-        <v>44</v>
+      <c r="F301" s="57">
+        <v>9</v>
+      </c>
+      <c r="G301" s="57">
+        <v>9</v>
       </c>
       <c r="H301" s="7" t="s">
         <v>34</v>
@@ -17830,26 +17863,26 @@
       <c r="A302" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B302" s="10" t="s">
-        <v>44</v>
+      <c r="B302" s="58">
+        <v>9</v>
       </c>
       <c r="C302" s="10">
         <v>5</v>
       </c>
-      <c r="D302" s="6" t="s">
-        <v>44</v>
+      <c r="D302" s="57">
+        <v>9</v>
       </c>
       <c r="E302" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F302" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G302" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H302" s="6" t="s">
-        <v>44</v>
+      <c r="F302" s="57">
+        <v>9</v>
+      </c>
+      <c r="G302" s="57">
+        <v>9</v>
+      </c>
+      <c r="H302" s="57">
+        <v>9</v>
       </c>
       <c r="I302" s="18">
         <f>PRODUCT($B$43,$C$38,$D$43,$E$43,$F$43)</f>
@@ -17872,17 +17905,17 @@
       <c r="A303" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B303" s="10" t="s">
-        <v>44</v>
+      <c r="B303" s="58">
+        <v>9</v>
       </c>
       <c r="C303" s="10">
         <v>5</v>
       </c>
-      <c r="D303" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E303" s="6" t="s">
-        <v>44</v>
+      <c r="D303" s="57">
+        <v>9</v>
+      </c>
+      <c r="E303" s="57">
+        <v>9</v>
       </c>
       <c r="F303" s="7" t="s">
         <v>34</v>
@@ -17914,17 +17947,17 @@
       <c r="A304" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B304" s="10" t="s">
-        <v>44</v>
+      <c r="B304" s="58">
+        <v>9</v>
       </c>
       <c r="C304" s="10">
         <v>5</v>
       </c>
-      <c r="D304" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E304" s="6" t="s">
-        <v>44</v>
+      <c r="D304" s="57">
+        <v>9</v>
+      </c>
+      <c r="E304" s="57">
+        <v>9</v>
       </c>
       <c r="F304" s="7" t="s">
         <v>34</v>
@@ -17932,8 +17965,8 @@
       <c r="G304" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H304" s="6" t="s">
-        <v>44</v>
+      <c r="H304" s="57">
+        <v>9</v>
       </c>
       <c r="I304" s="18">
         <f>PRODUCT($B$43,$C$43,$D$38,$E$38,$F$43)</f>
@@ -17956,23 +17989,23 @@
       <c r="A305" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B305" s="10" t="s">
-        <v>44</v>
+      <c r="B305" s="58">
+        <v>9</v>
       </c>
       <c r="C305" s="10">
         <v>5</v>
       </c>
-      <c r="D305" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E305" s="6" t="s">
-        <v>44</v>
+      <c r="D305" s="57">
+        <v>9</v>
+      </c>
+      <c r="E305" s="57">
+        <v>9</v>
       </c>
       <c r="F305" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G305" s="6" t="s">
-        <v>44</v>
+      <c r="G305" s="57">
+        <v>9</v>
       </c>
       <c r="H305" s="7" t="s">
         <v>34</v>
@@ -17998,26 +18031,26 @@
       <c r="A306" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B306" s="10" t="s">
-        <v>44</v>
+      <c r="B306" s="58">
+        <v>9</v>
       </c>
       <c r="C306" s="10">
         <v>5</v>
       </c>
-      <c r="D306" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E306" s="6" t="s">
-        <v>44</v>
+      <c r="D306" s="57">
+        <v>9</v>
+      </c>
+      <c r="E306" s="57">
+        <v>9</v>
       </c>
       <c r="F306" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G306" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H306" s="6" t="s">
-        <v>44</v>
+      <c r="G306" s="57">
+        <v>9</v>
+      </c>
+      <c r="H306" s="57">
+        <v>9</v>
       </c>
       <c r="I306" s="18">
         <f>PRODUCT($B$43,$C$43,$D$38,$E$43,$F$43)</f>
@@ -18040,20 +18073,20 @@
       <c r="A307" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B307" s="10" t="s">
-        <v>44</v>
+      <c r="B307" s="58">
+        <v>9</v>
       </c>
       <c r="C307" s="10">
         <v>5</v>
       </c>
-      <c r="D307" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E307" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F307" s="6" t="s">
-        <v>44</v>
+      <c r="D307" s="57">
+        <v>9</v>
+      </c>
+      <c r="E307" s="57">
+        <v>9</v>
+      </c>
+      <c r="F307" s="57">
+        <v>9</v>
       </c>
       <c r="G307" s="7" t="s">
         <v>34</v>
@@ -18082,26 +18115,26 @@
       <c r="A308" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B308" s="10" t="s">
-        <v>44</v>
+      <c r="B308" s="58">
+        <v>9</v>
       </c>
       <c r="C308" s="10">
         <v>5</v>
       </c>
-      <c r="D308" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E308" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F308" s="6" t="s">
-        <v>44</v>
+      <c r="D308" s="57">
+        <v>9</v>
+      </c>
+      <c r="E308" s="57">
+        <v>9</v>
+      </c>
+      <c r="F308" s="57">
+        <v>9</v>
       </c>
       <c r="G308" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H308" s="6" t="s">
-        <v>44</v>
+      <c r="H308" s="57">
+        <v>9</v>
       </c>
       <c r="I308" s="18">
         <f>PRODUCT($B$43,$C$43,$D$43,$E$38,$F$43)</f>
@@ -18124,23 +18157,23 @@
       <c r="A309" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B309" s="10" t="s">
-        <v>44</v>
+      <c r="B309" s="58">
+        <v>9</v>
       </c>
       <c r="C309" s="10">
         <v>5</v>
       </c>
-      <c r="D309" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E309" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F309" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G309" s="6" t="s">
-        <v>44</v>
+      <c r="D309" s="57">
+        <v>9</v>
+      </c>
+      <c r="E309" s="57">
+        <v>9</v>
+      </c>
+      <c r="F309" s="57">
+        <v>9</v>
+      </c>
+      <c r="G309" s="57">
+        <v>9</v>
       </c>
       <c r="H309" s="7" t="s">
         <v>34</v>
@@ -18166,8 +18199,8 @@
       <c r="A310" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B310" s="10" t="s">
-        <v>44</v>
+      <c r="B310" s="58">
+        <v>9</v>
       </c>
       <c r="C310" s="10">
         <v>4</v>
@@ -18208,8 +18241,8 @@
       <c r="A311" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B311" s="10" t="s">
-        <v>44</v>
+      <c r="B311" s="58">
+        <v>9</v>
       </c>
       <c r="C311" s="10">
         <v>4</v>
@@ -18223,8 +18256,8 @@
       <c r="F311" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G311" s="6" t="s">
-        <v>44</v>
+      <c r="G311" s="57">
+        <v>9</v>
       </c>
       <c r="H311" s="7" t="s">
         <v>164</v>
@@ -18250,8 +18283,8 @@
       <c r="A312" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B312" s="10" t="s">
-        <v>44</v>
+      <c r="B312" s="58">
+        <v>9</v>
       </c>
       <c r="C312" s="10">
         <v>4</v>
@@ -18262,8 +18295,8 @@
       <c r="E312" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F312" s="6" t="s">
-        <v>44</v>
+      <c r="F312" s="57">
+        <v>9</v>
       </c>
       <c r="G312" s="7" t="s">
         <v>34</v>
@@ -18292,8 +18325,8 @@
       <c r="A313" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B313" s="10" t="s">
-        <v>44</v>
+      <c r="B313" s="58">
+        <v>9</v>
       </c>
       <c r="C313" s="10">
         <v>4</v>
@@ -18304,11 +18337,11 @@
       <c r="E313" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F313" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G313" s="6" t="s">
-        <v>44</v>
+      <c r="F313" s="57">
+        <v>9</v>
+      </c>
+      <c r="G313" s="57">
+        <v>9</v>
       </c>
       <c r="H313" s="7" t="s">
         <v>164</v>
@@ -18334,8 +18367,8 @@
       <c r="A314" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B314" s="10" t="s">
-        <v>44</v>
+      <c r="B314" s="58">
+        <v>9</v>
       </c>
       <c r="C314" s="10">
         <v>4</v>
@@ -18343,8 +18376,8 @@
       <c r="D314" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E314" s="6" t="s">
-        <v>44</v>
+      <c r="E314" s="57">
+        <v>9</v>
       </c>
       <c r="F314" s="7" t="s">
         <v>34</v>
@@ -18376,8 +18409,8 @@
       <c r="A315" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B315" s="10" t="s">
-        <v>44</v>
+      <c r="B315" s="58">
+        <v>9</v>
       </c>
       <c r="C315" s="10">
         <v>4</v>
@@ -18385,14 +18418,14 @@
       <c r="D315" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E315" s="6" t="s">
-        <v>44</v>
+      <c r="E315" s="57">
+        <v>9</v>
       </c>
       <c r="F315" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G315" s="6" t="s">
-        <v>44</v>
+      <c r="G315" s="57">
+        <v>9</v>
       </c>
       <c r="H315" s="7" t="s">
         <v>164</v>
@@ -18418,8 +18451,8 @@
       <c r="A316" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B316" s="10" t="s">
-        <v>44</v>
+      <c r="B316" s="58">
+        <v>9</v>
       </c>
       <c r="C316" s="10">
         <v>4</v>
@@ -18427,11 +18460,11 @@
       <c r="D316" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E316" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F316" s="6" t="s">
-        <v>44</v>
+      <c r="E316" s="57">
+        <v>9</v>
+      </c>
+      <c r="F316" s="57">
+        <v>9</v>
       </c>
       <c r="G316" s="7" t="s">
         <v>34</v>
@@ -18460,8 +18493,8 @@
       <c r="A317" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B317" s="10" t="s">
-        <v>44</v>
+      <c r="B317" s="58">
+        <v>9</v>
       </c>
       <c r="C317" s="10">
         <v>4</v>
@@ -18469,14 +18502,14 @@
       <c r="D317" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E317" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F317" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G317" s="6" t="s">
-        <v>44</v>
+      <c r="E317" s="57">
+        <v>9</v>
+      </c>
+      <c r="F317" s="57">
+        <v>9</v>
+      </c>
+      <c r="G317" s="57">
+        <v>9</v>
       </c>
       <c r="H317" s="7" t="s">
         <v>164</v>
@@ -18502,14 +18535,14 @@
       <c r="A318" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B318" s="10" t="s">
-        <v>44</v>
+      <c r="B318" s="58">
+        <v>9</v>
       </c>
       <c r="C318" s="10">
         <v>4</v>
       </c>
-      <c r="D318" s="6" t="s">
-        <v>44</v>
+      <c r="D318" s="57">
+        <v>9</v>
       </c>
       <c r="E318" s="7" t="s">
         <v>34</v>
@@ -18544,14 +18577,14 @@
       <c r="A319" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B319" s="10" t="s">
-        <v>44</v>
+      <c r="B319" s="58">
+        <v>9</v>
       </c>
       <c r="C319" s="10">
         <v>4</v>
       </c>
-      <c r="D319" s="6" t="s">
-        <v>44</v>
+      <c r="D319" s="57">
+        <v>9</v>
       </c>
       <c r="E319" s="7" t="s">
         <v>34</v>
@@ -18559,8 +18592,8 @@
       <c r="F319" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G319" s="6" t="s">
-        <v>44</v>
+      <c r="G319" s="57">
+        <v>9</v>
       </c>
       <c r="H319" s="7" t="s">
         <v>164</v>
@@ -18586,20 +18619,20 @@
       <c r="A320" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B320" s="10" t="s">
-        <v>44</v>
+      <c r="B320" s="58">
+        <v>9</v>
       </c>
       <c r="C320" s="10">
         <v>4</v>
       </c>
-      <c r="D320" s="6" t="s">
-        <v>44</v>
+      <c r="D320" s="57">
+        <v>9</v>
       </c>
       <c r="E320" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F320" s="6" t="s">
-        <v>44</v>
+      <c r="F320" s="57">
+        <v>9</v>
       </c>
       <c r="G320" s="7" t="s">
         <v>34</v>
@@ -18628,23 +18661,23 @@
       <c r="A321" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B321" s="10" t="s">
-        <v>44</v>
+      <c r="B321" s="58">
+        <v>9</v>
       </c>
       <c r="C321" s="10">
         <v>4</v>
       </c>
-      <c r="D321" s="6" t="s">
-        <v>44</v>
+      <c r="D321" s="57">
+        <v>9</v>
       </c>
       <c r="E321" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F321" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G321" s="6" t="s">
-        <v>44</v>
+      <c r="F321" s="57">
+        <v>9</v>
+      </c>
+      <c r="G321" s="57">
+        <v>9</v>
       </c>
       <c r="H321" s="7" t="s">
         <v>164</v>
@@ -18670,17 +18703,17 @@
       <c r="A322" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B322" s="10" t="s">
-        <v>44</v>
+      <c r="B322" s="58">
+        <v>9</v>
       </c>
       <c r="C322" s="10">
         <v>4</v>
       </c>
-      <c r="D322" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E322" s="6" t="s">
-        <v>44</v>
+      <c r="D322" s="57">
+        <v>9</v>
+      </c>
+      <c r="E322" s="57">
+        <v>9</v>
       </c>
       <c r="F322" s="7" t="s">
         <v>34</v>
@@ -18712,23 +18745,23 @@
       <c r="A323" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B323" s="10" t="s">
-        <v>44</v>
+      <c r="B323" s="58">
+        <v>9</v>
       </c>
       <c r="C323" s="10">
         <v>4</v>
       </c>
-      <c r="D323" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E323" s="6" t="s">
-        <v>44</v>
+      <c r="D323" s="57">
+        <v>9</v>
+      </c>
+      <c r="E323" s="57">
+        <v>9</v>
       </c>
       <c r="F323" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G323" s="6" t="s">
-        <v>44</v>
+      <c r="G323" s="57">
+        <v>9</v>
       </c>
       <c r="H323" s="7" t="s">
         <v>164</v>
@@ -18754,20 +18787,20 @@
       <c r="A324" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B324" s="10" t="s">
-        <v>44</v>
+      <c r="B324" s="58">
+        <v>9</v>
       </c>
       <c r="C324" s="10">
         <v>4</v>
       </c>
-      <c r="D324" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E324" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F324" s="6" t="s">
-        <v>44</v>
+      <c r="D324" s="57">
+        <v>9</v>
+      </c>
+      <c r="E324" s="57">
+        <v>9</v>
+      </c>
+      <c r="F324" s="57">
+        <v>9</v>
       </c>
       <c r="G324" s="7" t="s">
         <v>34</v>
@@ -18796,8 +18829,8 @@
       <c r="A325" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B325" s="10" t="s">
-        <v>44</v>
+      <c r="B325" s="58">
+        <v>9</v>
       </c>
       <c r="C325" s="10">
         <v>3</v>
@@ -18838,8 +18871,8 @@
       <c r="A326" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B326" s="10" t="s">
-        <v>44</v>
+      <c r="B326" s="58">
+        <v>9</v>
       </c>
       <c r="C326" s="10">
         <v>3</v>
@@ -18850,8 +18883,8 @@
       <c r="E326" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F326" s="6" t="s">
-        <v>44</v>
+      <c r="F326" s="57">
+        <v>9</v>
       </c>
       <c r="G326" s="7" t="s">
         <v>164</v>
@@ -18880,8 +18913,8 @@
       <c r="A327" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B327" s="10" t="s">
-        <v>44</v>
+      <c r="B327" s="58">
+        <v>9</v>
       </c>
       <c r="C327" s="10">
         <v>3</v>
@@ -18889,8 +18922,8 @@
       <c r="D327" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E327" s="6" t="s">
-        <v>44</v>
+      <c r="E327" s="57">
+        <v>9</v>
       </c>
       <c r="F327" s="7" t="s">
         <v>34</v>
@@ -18922,8 +18955,8 @@
       <c r="A328" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B328" s="10" t="s">
-        <v>44</v>
+      <c r="B328" s="58">
+        <v>9</v>
       </c>
       <c r="C328" s="10">
         <v>3</v>
@@ -18931,11 +18964,11 @@
       <c r="D328" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E328" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F328" s="6" t="s">
-        <v>44</v>
+      <c r="E328" s="57">
+        <v>9</v>
+      </c>
+      <c r="F328" s="57">
+        <v>9</v>
       </c>
       <c r="G328" s="7" t="s">
         <v>164</v>
@@ -18964,14 +18997,14 @@
       <c r="A329" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B329" s="10" t="s">
-        <v>44</v>
+      <c r="B329" s="58">
+        <v>9</v>
       </c>
       <c r="C329" s="10">
         <v>3</v>
       </c>
-      <c r="D329" s="6" t="s">
-        <v>44</v>
+      <c r="D329" s="57">
+        <v>9</v>
       </c>
       <c r="E329" s="7" t="s">
         <v>34</v>
@@ -19006,20 +19039,20 @@
       <c r="A330" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B330" s="10" t="s">
-        <v>44</v>
+      <c r="B330" s="58">
+        <v>9</v>
       </c>
       <c r="C330" s="10">
         <v>3</v>
       </c>
-      <c r="D330" s="6" t="s">
-        <v>44</v>
+      <c r="D330" s="57">
+        <v>9</v>
       </c>
       <c r="E330" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F330" s="6" t="s">
-        <v>44</v>
+      <c r="F330" s="57">
+        <v>9</v>
       </c>
       <c r="G330" s="7" t="s">
         <v>164</v>
@@ -19048,17 +19081,17 @@
       <c r="A331" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B331" s="10" t="s">
-        <v>44</v>
+      <c r="B331" s="58">
+        <v>9</v>
       </c>
       <c r="C331" s="10">
         <v>3</v>
       </c>
-      <c r="D331" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E331" s="6" t="s">
-        <v>44</v>
+      <c r="D331" s="57">
+        <v>9</v>
+      </c>
+      <c r="E331" s="57">
+        <v>9</v>
       </c>
       <c r="F331" s="7" t="s">
         <v>34</v>
